--- a/files/九龙-何文田-天铸 (第2期).xlsx
+++ b/files/九龙-何文田-天铸 (第2期).xlsx
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2866</v>
+        <v>2957</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>2442</v>
+        <v>2539</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>130758500</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>53546</v>
+        <v>51500</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>130758500</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>53546</v>
+        <v>51500</v>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>2493</v>
+        <v>2598</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1207,7 +1207,7 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1731</v>
+        <v>1823</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>74784440</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>43203</v>
+        <v>41023</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>74784440</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>43203</v>
+        <v>41023</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
         <v>77515500</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>40584</v>
+        <v>38393</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
         <v>77515500</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>40584</v>
+        <v>38393</v>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         <v>84798000</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>44397</v>
+        <v>42000</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>84798000</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>44397</v>
+        <v>42000</v>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1731</v>
+        <v>1823</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
@@ -1719,7 +1719,7 @@
         <v>78540300</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>45373</v>
+        <v>43083</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>78540300</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>45373</v>
+        <v>43083</v>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
@@ -1765,7 +1765,7 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
@@ -1781,7 +1781,7 @@
         <v>72269000</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>37837</v>
+        <v>35794</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
@@ -1792,7 +1792,7 @@
         <v>72269000</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>37837</v>
+        <v>35794</v>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1731</v>
+        <v>1823</v>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
@@ -1967,7 +1967,7 @@
         <v>77538600</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>44794</v>
+        <v>42534</v>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>77538600</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>44794</v>
+        <v>42534</v>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -2029,7 +2029,7 @@
         <v>86098888</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>45078</v>
+        <v>42644</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>86098888</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>45078</v>
+        <v>42644</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>85720000</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>44880</v>
+        <v>42457</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         <v>85720000</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>44880</v>
+        <v>42457</v>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
@@ -2509,7 +2509,7 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>76722000</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>40169</v>
+        <v>38000</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2536,7 +2536,7 @@
         <v>76722000</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>40169</v>
+        <v>38000</v>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -3021,7 +3021,7 @@
         <v>80866000</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>42338</v>
+        <v>40053</v>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>80866000</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>42338</v>
+        <v>40053</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1910</v>
+        <v>2019</v>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
@@ -3765,7 +3765,7 @@
         <v>55880600</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>29257</v>
+        <v>27677</v>
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>55880600</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>29257</v>
+        <v>27677</v>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>863</v>
+        <v>965</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -4323,7 +4323,7 @@
         <v>18326000</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>21235</v>
+        <v>18991</v>
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
@@ -4334,7 +4334,7 @@
         <v>18326000</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>21235</v>
+        <v>18991</v>
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1045</v>
+        <v>1138</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>20703700</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>19812</v>
+        <v>18193</v>
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>20703700</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>19812</v>
+        <v>18193</v>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>2337</v>
+        <v>2336</v>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>54364100</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>23262</v>
+        <v>23272</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
@@ -4582,7 +4582,7 @@
         <v>54364100</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>23262</v>
+        <v>23272</v>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
@@ -4617,7 +4617,7 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>2065</v>
+        <v>2064</v>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>46739500</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>22634</v>
+        <v>22645</v>
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
@@ -4644,7 +4644,7 @@
         <v>46739500</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>22634</v>
+        <v>22645</v>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>2079</v>
+        <v>2173</v>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>75094800</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>36121</v>
+        <v>34558</v>
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
@@ -4768,7 +4768,7 @@
         <v>75094800</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>36121</v>
+        <v>34558</v>
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>2681</v>
+        <v>2774</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4819,7 +4819,7 @@
         <v>148310000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>55319</v>
+        <v>53464</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>148310000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>55319</v>
+        <v>53464</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>2026</v>
+        <v>2128</v>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>83483500</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>41206</v>
+        <v>39231</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>83483500</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>41206</v>
+        <v>39231</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>2199</v>
+        <v>2278</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -5129,7 +5129,7 @@
         <v>113910000</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>51801</v>
+        <v>50004</v>
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>113910000</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>51801</v>
+        <v>50004</v>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="E76" s="4" t="n">
-        <v>1606</v>
+        <v>1708</v>
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
@@ -5315,7 +5315,7 @@
         <v>71978700</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>44819</v>
+        <v>42142</v>
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>71978700</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>44819</v>
+        <v>42142</v>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         </is>
       </c>
       <c r="E80" s="4" t="n">
-        <v>1606</v>
+        <v>1708</v>
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
@@ -5563,7 +5563,7 @@
         <v>74639600</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>46475</v>
+        <v>43700</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>74639600</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>46475</v>
+        <v>43700</v>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         </is>
       </c>
       <c r="E81" s="4" t="n">
-        <v>1646</v>
+        <v>1738</v>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
@@ -5625,7 +5625,7 @@
         <v>81825000</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>49711</v>
+        <v>47080</v>
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>81825000</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>49711</v>
+        <v>47080</v>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         </is>
       </c>
       <c r="E88" s="4" t="n">
-        <v>1606</v>
+        <v>1708</v>
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         <v>70680000</v>
       </c>
       <c r="I88" s="5" t="n">
-        <v>44010</v>
+        <v>41382</v>
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>70680000</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>44010</v>
+        <v>41382</v>
       </c>
       <c r="M88" s="3" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         </is>
       </c>
       <c r="E89" s="4" t="n">
-        <v>1646</v>
+        <v>1738</v>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
         <v>63980000</v>
       </c>
       <c r="I89" s="5" t="n">
-        <v>38870</v>
+        <v>36812</v>
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>63980000</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>38870</v>
+        <v>36812</v>
       </c>
       <c r="M89" s="3" t="inlineStr">
         <is>
@@ -6663,7 +6663,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>1142</v>
+        <v>1237</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -6679,7 +6679,7 @@
         <v>34819200</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>30490</v>
+        <v>28148</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>34819200</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>30490</v>
+        <v>28148</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         </is>
       </c>
       <c r="E100" s="4" t="n">
-        <v>1606</v>
+        <v>1708</v>
       </c>
       <c r="F100" s="3" t="inlineStr">
         <is>
@@ -6803,7 +6803,7 @@
         <v>68290000</v>
       </c>
       <c r="I100" s="5" t="n">
-        <v>42522</v>
+        <v>39982</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>68290000</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>42522</v>
+        <v>39982</v>
       </c>
       <c r="M100" s="3" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="E101" s="4" t="n">
-        <v>1646</v>
+        <v>1738</v>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
@@ -6865,7 +6865,7 @@
         <v>79109600</v>
       </c>
       <c r="I101" s="5" t="n">
-        <v>48062</v>
+        <v>45518</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>79109600</v>
       </c>
       <c r="L101" s="5" t="n">
-        <v>48062</v>
+        <v>45518</v>
       </c>
       <c r="M101" s="3" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         </is>
       </c>
       <c r="E102" s="4" t="n">
-        <v>1142</v>
+        <v>1237</v>
       </c>
       <c r="F102" s="3" t="inlineStr">
         <is>
@@ -6927,7 +6927,7 @@
         <v>34192400</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>29941</v>
+        <v>27641</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>34192400</v>
       </c>
       <c r="L102" s="5" t="n">
-        <v>29941</v>
+        <v>27641</v>
       </c>
       <c r="M102" s="3" t="inlineStr">
         <is>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="E131" s="4" t="n">
-        <v>1324</v>
+        <v>1412</v>
       </c>
       <c r="F131" s="3" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>25970800</v>
       </c>
       <c r="I131" s="5" t="n">
-        <v>19615</v>
+        <v>18393</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -8736,7 +8736,7 @@
         <v>25970800</v>
       </c>
       <c r="L131" s="5" t="n">
-        <v>19615</v>
+        <v>18393</v>
       </c>
       <c r="M131" s="3" t="inlineStr">
         <is>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="E133" s="4" t="n">
-        <v>1630</v>
+        <v>1722</v>
       </c>
       <c r="F133" s="3" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>35028888</v>
       </c>
       <c r="I133" s="5" t="n">
-        <v>21490</v>
+        <v>20342</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -8860,7 +8860,7 @@
         <v>35028888</v>
       </c>
       <c r="L133" s="5" t="n">
-        <v>21490</v>
+        <v>20342</v>
       </c>
       <c r="M133" s="3" t="inlineStr">
         <is>
@@ -8957,7 +8957,7 @@
         </is>
       </c>
       <c r="E135" s="4" t="n">
-        <v>1990</v>
+        <v>2090</v>
       </c>
       <c r="F135" s="3" t="inlineStr">
         <is>
@@ -8973,7 +8973,7 @@
         <v>125400000</v>
       </c>
       <c r="I135" s="5" t="n">
-        <v>63015</v>
+        <v>60000</v>
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
@@ -8984,7 +8984,7 @@
         <v>125400000</v>
       </c>
       <c r="L135" s="5" t="n">
-        <v>63015</v>
+        <v>60000</v>
       </c>
       <c r="M135" s="3" t="inlineStr">
         <is>
@@ -9019,7 +9019,7 @@
         </is>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2681</v>
+        <v>2774</v>
       </c>
       <c r="F136" s="3" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>152267800</v>
       </c>
       <c r="I136" s="5" t="n">
-        <v>56795</v>
+        <v>54891</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>152267800</v>
       </c>
       <c r="L136" s="5" t="n">
-        <v>56795</v>
+        <v>54891</v>
       </c>
       <c r="M136" s="3" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="E140" s="4" t="n">
-        <v>2199</v>
+        <v>2278</v>
       </c>
       <c r="F140" s="3" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>142602800</v>
       </c>
       <c r="I140" s="5" t="n">
-        <v>64849</v>
+        <v>62600</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         <v>142602800</v>
       </c>
       <c r="L140" s="5" t="n">
-        <v>64849</v>
+        <v>62600</v>
       </c>
       <c r="M140" s="3" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="E141" s="4" t="n">
-        <v>2265</v>
+        <v>2361</v>
       </c>
       <c r="F141" s="3" t="inlineStr">
         <is>
@@ -9345,7 +9345,7 @@
         <v>155826000</v>
       </c>
       <c r="I141" s="5" t="n">
-        <v>68797</v>
+        <v>66000</v>
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>155826000</v>
       </c>
       <c r="L141" s="5" t="n">
-        <v>68797</v>
+        <v>66000</v>
       </c>
       <c r="M141" s="3" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         </is>
       </c>
       <c r="E204" s="4" t="n">
-        <v>2733</v>
+        <v>2826</v>
       </c>
       <c r="F204" s="3" t="inlineStr">
         <is>
@@ -13251,7 +13251,7 @@
         <v>213912000</v>
       </c>
       <c r="I204" s="5" t="n">
-        <v>78270</v>
+        <v>75694</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>213912000</v>
       </c>
       <c r="L204" s="5" t="n">
-        <v>78270</v>
+        <v>75694</v>
       </c>
       <c r="M204" s="3" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         </is>
       </c>
       <c r="E205" s="4" t="n">
-        <v>2044</v>
+        <v>2130</v>
       </c>
       <c r="F205" s="3" t="inlineStr">
         <is>
@@ -13313,7 +13313,7 @@
         <v>128601000</v>
       </c>
       <c r="I205" s="5" t="n">
-        <v>62916</v>
+        <v>60376</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -13324,7 +13324,7 @@
         <v>128601000</v>
       </c>
       <c r="L205" s="5" t="n">
-        <v>62916</v>
+        <v>60376</v>
       </c>
       <c r="M205" s="3" t="inlineStr">
         <is>
@@ -13607,7 +13607,7 @@
         </is>
       </c>
       <c r="E210" s="4" t="n">
-        <v>1221</v>
+        <v>1316</v>
       </c>
       <c r="F210" s="3" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>39468600</v>
       </c>
       <c r="I210" s="5" t="n">
-        <v>32325</v>
+        <v>29991</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>39468600</v>
       </c>
       <c r="L210" s="5" t="n">
-        <v>32325</v>
+        <v>29991</v>
       </c>
       <c r="M210" s="3" t="inlineStr">
         <is>
@@ -13855,7 +13855,7 @@
         </is>
       </c>
       <c r="E214" s="4" t="n">
-        <v>1221</v>
+        <v>1316</v>
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>38962000</v>
       </c>
       <c r="I214" s="5" t="n">
-        <v>31910</v>
+        <v>29606</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>38962000</v>
       </c>
       <c r="L214" s="5" t="n">
-        <v>31910</v>
+        <v>29606</v>
       </c>
       <c r="M214" s="3" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         </is>
       </c>
       <c r="E230" s="4" t="n">
-        <v>1221</v>
+        <v>1316</v>
       </c>
       <c r="F230" s="3" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>37000500</v>
       </c>
       <c r="I230" s="5" t="n">
-        <v>30303</v>
+        <v>28116</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -14874,7 +14874,7 @@
         <v>37000500</v>
       </c>
       <c r="L230" s="5" t="n">
-        <v>30303</v>
+        <v>28116</v>
       </c>
       <c r="M230" s="3" t="inlineStr">
         <is>
@@ -15219,7 +15219,7 @@
         </is>
       </c>
       <c r="E236" s="4" t="n">
-        <v>1065</v>
+        <v>1160</v>
       </c>
       <c r="F236" s="3" t="inlineStr">
         <is>
@@ -15235,7 +15235,7 @@
         <v>35290300</v>
       </c>
       <c r="I236" s="5" t="n">
-        <v>33136</v>
+        <v>30423</v>
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>35290300</v>
       </c>
       <c r="L236" s="5" t="n">
-        <v>33136</v>
+        <v>30423</v>
       </c>
       <c r="M236" s="3" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         </is>
       </c>
       <c r="E248" s="4" t="n">
-        <v>1065</v>
+        <v>1160</v>
       </c>
       <c r="F248" s="3" t="inlineStr">
         <is>
@@ -15979,7 +15979,7 @@
         <v>33078400</v>
       </c>
       <c r="I248" s="5" t="n">
-        <v>31060</v>
+        <v>28516</v>
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
@@ -15990,7 +15990,7 @@
         <v>33078400</v>
       </c>
       <c r="L248" s="5" t="n">
-        <v>31060</v>
+        <v>28516</v>
       </c>
       <c r="M248" s="3" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         </is>
       </c>
       <c r="E250" s="4" t="n">
-        <v>1221</v>
+        <v>1316</v>
       </c>
       <c r="F250" s="3" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>33606900</v>
       </c>
       <c r="I250" s="5" t="n">
-        <v>27524</v>
+        <v>25537</v>
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
@@ -16114,7 +16114,7 @@
         <v>33606900</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>27524</v>
+        <v>25537</v>
       </c>
       <c r="M250" s="3" t="inlineStr">
         <is>
@@ -16459,7 +16459,7 @@
         </is>
       </c>
       <c r="E256" s="4" t="n">
-        <v>1065</v>
+        <v>1160</v>
       </c>
       <c r="F256" s="3" t="inlineStr">
         <is>
@@ -16475,7 +16475,7 @@
         <v>30454700</v>
       </c>
       <c r="I256" s="5" t="n">
-        <v>28596</v>
+        <v>26254</v>
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
@@ -16486,7 +16486,7 @@
         <v>30454700</v>
       </c>
       <c r="L256" s="5" t="n">
-        <v>28596</v>
+        <v>26254</v>
       </c>
       <c r="M256" s="3" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         </is>
       </c>
       <c r="E266" s="4" t="n">
-        <v>1221</v>
+        <v>1316</v>
       </c>
       <c r="F266" s="3" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>22105600</v>
       </c>
       <c r="I266" s="5" t="n">
-        <v>18105</v>
+        <v>16798</v>
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
@@ -17106,7 +17106,7 @@
         <v>22105600</v>
       </c>
       <c r="L266" s="5" t="n">
-        <v>18105</v>
+        <v>16798</v>
       </c>
       <c r="M266" s="3" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         </is>
       </c>
       <c r="E271" s="4" t="n">
-        <v>1150</v>
+        <v>1249</v>
       </c>
       <c r="F271" s="3" t="inlineStr">
         <is>
@@ -17405,7 +17405,7 @@
         <v>36231000</v>
       </c>
       <c r="I271" s="5" t="n">
-        <v>31505</v>
+        <v>29008</v>
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
@@ -17416,7 +17416,7 @@
         <v>36231000</v>
       </c>
       <c r="L271" s="5" t="n">
-        <v>31505</v>
+        <v>29008</v>
       </c>
       <c r="M271" s="3" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         </is>
       </c>
       <c r="E272" s="4" t="n">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="F272" s="3" t="inlineStr">
         <is>
@@ -17467,7 +17467,7 @@
         <v>62774600</v>
       </c>
       <c r="I272" s="5" t="n">
-        <v>31865</v>
+        <v>31881</v>
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>62774600</v>
       </c>
       <c r="L272" s="5" t="n">
-        <v>31865</v>
+        <v>31881</v>
       </c>
       <c r="M272" s="3" t="inlineStr">
         <is>
@@ -17684,7 +17684,7 @@
       </c>
       <c r="B5" s="20" t="inlineStr">
         <is>
-          <t>A | 2866呎 (4+房)
+          <t>A | 2957呎 (4+房)
 -
 -
 (待售)</t>
@@ -17709,7 +17709,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>A | 2493呎 (4+房)
+          <t>A | 2598呎 (4+房)
 -
 -
 (待售)</t>
@@ -17717,9 +17717,9 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>B | 2442呎 (4+房)
+          <t>B | 2539呎 (4+房)
 $13076万
-$53,546/呎
+$51,500/呎
 (24年-05月-27日)</t>
         </is>
       </c>
@@ -17741,17 +17741,17 @@
       </c>
       <c r="B7" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $7752万
-$40,584/呎
+$38,393/呎
 (25年-11月-13日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1731呎 (4+房)
+          <t>B | 1823呎 (4+房)
 $7478万
-$43,203/呎
+$41,023/呎
 (25年-10月-28日)</t>
         </is>
       </c>
@@ -17780,9 +17780,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $8480万
-$44,397/呎
+$42,000/呎
 (19年-04月-04日)</t>
         </is>
       </c>
@@ -17819,17 +17819,17 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $7227万
-$37,837/呎
+$35,794/呎
 (25年-08月-20日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 1731呎 (4+房)
+          <t>B | 1823呎 (4+房)
 $7854万
-$45,373/呎
+$43,083/呎
 (23年-03月-21日)</t>
         </is>
       </c>
@@ -17858,17 +17858,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $8610万
-$45,078/呎
+$42,644/呎
 (23年-03月-06日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1731呎 (4+房)
+          <t>B | 1823呎 (4+房)
 $7754万
-$44,794/呎
+$42,534/呎
 (23年-04月-04日)</t>
         </is>
       </c>
@@ -17897,9 +17897,9 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $8572万
-$44,880/呎
+$42,457/呎
 (23年-03月-03日)</t>
         </is>
       </c>
@@ -17936,9 +17936,9 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $7672万
-$40,169/呎
+$38,000/呎
 (19年-04月-04日)</t>
         </is>
       </c>
@@ -18014,9 +18014,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $8087万
-$42,338/呎
+$40,053/呎
 (19年-04月-10日)</t>
         </is>
       </c>
@@ -18131,9 +18131,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 1910呎 (4+房)
+          <t>A | 2019呎 (4+房)
 $5588万
-$29,257/呎
+$27,677/呎
 (16年-05月-18日)</t>
         </is>
       </c>
@@ -18264,17 +18264,17 @@
       </c>
       <c r="D20" s="22" t="inlineStr">
         <is>
-          <t>C | 1045呎 (3房)
+          <t>C | 1138呎 (3房)
 $2070万
-$19,812/呎
+$18,193/呎
 (16年-04月-25日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>D | 863呎 (3房)
+          <t>D | 965呎 (3房)
 $1833万
-$21,235/呎
+$18,991/呎
 (16年-05月-10日)</t>
         </is>
       </c>
@@ -18287,17 +18287,17 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>A | 2065呎 (3房)
+          <t>A | 2064呎 (3房)
 $4674万
-$22,634/呎
+$22,645/呎
 (16年-04月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>B | 2337呎 (4+房)
+          <t>B | 2336呎 (4+房)
 $5436万
-$23,262/呎
+$23,272/呎
 (16年-04月-15日)</t>
         </is>
       </c>
@@ -18435,18 +18435,18 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 2681呎 (4+房)
+          <t>A | 2774呎 (4+房)
 $14831万
-$55,319/呎
+$53,464/呎
 (25年-08月-12日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>C | 2079呎 (3房)
+          <t>C | 2173呎 (3房)
 $7509万
-$36,121/呎
+$34,558/呎
 (16年-04月-26日)</t>
         </is>
       </c>
@@ -18469,9 +18469,9 @@
       <c r="C6" s="21" t="inlineStr"/>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>C | 2026呎 (4+房)
+          <t>C | 2128呎 (4+房)
 $8348万
-$41,206/呎
+$39,231/呎
 (16年-05月-11日)</t>
         </is>
       </c>
@@ -18510,9 +18510,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 2199呎 (4+房)
+          <t>A | 2278呎 (4+房)
 $11391万
-$51,801/呎
+$50,004/呎
 (24年-04月-29日)</t>
         </is>
       </c>
@@ -18543,9 +18543,9 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>B | 1606呎 (4+房)
+          <t>B | 1708呎 (4+房)
 $7198万
-$44,819/呎
+$42,142/呎
 (16年-04月-21日)</t>
         </is>
       </c>
@@ -18574,17 +18574,17 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 1646呎 (4+房)
+          <t>A | 1738呎 (4+房)
 $8182万
-$49,711/呎
+$47,080/呎
 (19年-01月-28日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>B | 1606呎 (4+房)
+          <t>B | 1708呎 (4+房)
 $7464万
-$46,475/呎
+$43,700/呎
 (19年-03月-04日)</t>
         </is>
       </c>
@@ -18652,17 +18652,17 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>A | 1646呎 (4+房)
+          <t>A | 1738呎 (4+房)
 $6398万
-$38,870/呎
+$36,812/呎
 (24年-10月-15日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1606呎 (4+房)
+          <t>B | 1708呎 (4+房)
 $7068万
-$44,010/呎
+$41,382/呎
 (26年-01月-07日)</t>
         </is>
       </c>
@@ -18769,17 +18769,17 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 1646呎 (4+房)
+          <t>A | 1738呎 (4+房)
 $7911万
-$48,062/呎
+$45,518/呎
 (19年-02月-18日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
         <is>
-          <t>B | 1606呎 (4+房)
+          <t>B | 1708呎 (4+房)
 $6829万
-$42,522/呎
+$39,982/呎
 (19年-08月-07日)</t>
         </is>
       </c>
@@ -18793,9 +18793,9 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>D | 1142呎 (3房)
+          <t>D | 1237呎 (3房)
 $3482万
-$30,490/呎
+$28,148/呎
 (16年-04月-20日)</t>
         </is>
       </c>
@@ -18832,9 +18832,9 @@
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>D | 1142呎 (3房)
+          <t>D | 1237呎 (3房)
 $3419万
-$29,941/呎
+$27,641/呎
 (16年-04月-19日)</t>
         </is>
       </c>
@@ -19081,9 +19081,9 @@
       </c>
       <c r="B23" s="22" t="inlineStr">
         <is>
-          <t>A | 1630呎 (4+房)
+          <t>A | 1722呎 (4+房)
 $3503万
-$21,490/呎
+$20,342/呎
 (24年-05月-29日)</t>
         </is>
       </c>
@@ -19097,9 +19097,9 @@
       </c>
       <c r="D23" s="22" t="inlineStr">
         <is>
-          <t>C | 1324呎 (4+房)
+          <t>C | 1412呎 (4+房)
 $2597万
-$19,615/呎
+$18,393/呎
 (16年-04月-27日)</t>
         </is>
       </c>
@@ -19243,18 +19243,18 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 2681呎 (4+房)
+          <t>A | 2774呎 (4+房)
 $15227万
-$56,795/呎
+$54,891/呎
 (25年-11月-25日)</t>
         </is>
       </c>
       <c r="C5" s="21" t="inlineStr"/>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>C | 1990呎 (3房)
+          <t>C | 2090呎 (3房)
 $12540万
-$63,015/呎
+$60,000/呎
 (19年-11月-04日)</t>
         </is>
       </c>
@@ -19318,17 +19318,17 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 2265呎 (4+房)
+          <t>A | 2361呎 (4+房)
 $15583万
-$68,797/呎
+$66,000/呎
 (19年-07月-30日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 2199呎 (4+房)
+          <t>B | 2278呎 (4+房)
 $14260万
-$64,849/呎
+$62,600/呎
 (19年-02月-21日)</t>
         </is>
       </c>
@@ -20051,9 +20051,9 @@
       </c>
       <c r="B5" s="22" t="inlineStr">
         <is>
-          <t>A | 2733呎 (4+房)
+          <t>A | 2826呎 (4+房)
 $21391万
-$78,270/呎
+$75,694/呎
 (19年-02月-15日)</t>
         </is>
       </c>
@@ -20099,9 +20099,9 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>C | 2044呎 (3房)
+          <t>C | 2130呎 (3房)
 $12860万
-$62,916/呎
+$60,376/呎
 (20年-02月-21日)</t>
         </is>
       </c>
@@ -20123,9 +20123,9 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>B | 1221呎 (4+房)
+          <t>B | 1316呎 (4+房)
 $3947万
-$32,325/呎
+$29,991/呎
 (16年-05月-05日)</t>
         </is>
       </c>
@@ -20162,9 +20162,9 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>B | 1221呎 (4+房)
+          <t>B | 1316呎 (4+房)
 $3896万
-$31,910/呎
+$29,606/呎
 (16年-04月-29日)</t>
         </is>
       </c>
@@ -20318,9 +20318,9 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>B | 1221呎 (4+房)
+          <t>B | 1316呎 (4+房)
 $3700万
-$30,303/呎
+$28,116/呎
 (16年-05月-17日)</t>
         </is>
       </c>
@@ -20412,9 +20412,9 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>D | 1065呎 (3房)
+          <t>D | 1160呎 (3房)
 $3529万
-$33,136/呎
+$30,423/呎
 (16年-05月-13日)</t>
         </is>
       </c>
@@ -20513,9 +20513,9 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>B | 1221呎 (4+房)
+          <t>B | 1316呎 (4+房)
 $3361万
-$27,524/呎
+$25,537/呎
 (16年-04月-15日)</t>
         </is>
       </c>
@@ -20529,9 +20529,9 @@
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>D | 1065呎 (3房)
+          <t>D | 1160呎 (3房)
 $3308万
-$31,060/呎
+$28,516/呎
 (16年-05月-12日)</t>
         </is>
       </c>
@@ -20607,9 +20607,9 @@
       </c>
       <c r="E19" s="22" t="inlineStr">
         <is>
-          <t>D | 1065呎 (3房)
+          <t>D | 1160呎 (3房)
 $3045万
-$28,596/呎
+$26,254/呎
 (16年-05月-18日)</t>
         </is>
       </c>
@@ -20669,9 +20669,9 @@
       </c>
       <c r="C21" s="22" t="inlineStr">
         <is>
-          <t>B | 1221呎 (4+房)
+          <t>B | 1316呎 (4+房)
 $2211万
-$18,105/呎
+$16,798/呎
 (16年-04月-27日)</t>
         </is>
       </c>
@@ -20700,9 +20700,9 @@
       </c>
       <c r="B22" s="22" t="inlineStr">
         <is>
-          <t>A | 1150呎 (4+房)
+          <t>A | 1249呎 (4+房)
 $3623万
-$31,505/呎
+$29,008/呎
 (24年-05月-30日)</t>
         </is>
       </c>
@@ -20747,9 +20747,9 @@
       </c>
       <c r="C23" s="22" t="inlineStr">
         <is>
-          <t>B | 1970呎 (2房)
+          <t>B | 1969呎 (2房)
 $6277万
-$31,865/呎
+$31,881/呎
 (16年-05月-19日)</t>
         </is>
       </c>
